--- a/ac.xlsx
+++ b/ac.xlsx
@@ -337,82 +337,127 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:1">
+      <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:1">
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:1">
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:1">
+      <c r="B9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:1">
+      <c r="B10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:1">
+      <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:1">
+      <c r="B12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:1">
+      <c r="B13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:1">
+      <c r="B14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15">
         <v>10</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
